--- a/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>César joue dans sa chambre. Papa est près de la fenêtre. César a des voitures. Les voitures sont rouges et bleues. César fait une route. Les voitures font vroom. Puis le jeu est fini. Papa dit : c'est l'heure de ranger. César prend une voiture. Il la met dans la caisse. Il prend une autre voiture. Il la met dans la caisse. Encore une voiture. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse. Papa dit : merci César. César ferme la caisse. Ça fait toc. Le sol est libre. Papa sourit.</t>
+          <t>César joue dans sa chambre. Papa est près de la fenêtre. César a des voitures. Les voitures sont rouges et bleues. César fait une route. Les voitures font vroom. Puis le jeu est fini. C'est l'heure de ranger. César prend une voiture. Il la met dans la caisse. Il prend une autre voiture. Il la met dans la caisse. Encore une voiture. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse. Merci César. César ferme la caisse. Ça fait toc. Le sol est libre. Papa sourit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|César joue dans sa chambre. Papa est près de la fenêtre. César a des voitures. Les voitures sont rouges et bleues. César fait une route. Les voitures font vroom. Puis le jeu est fini.
+papa|C'est l'heure de ranger.
+narrateur|César prend une voiture. Il la met dans la caisse. Il prend une autre voiture. Il la met dans la caisse. Encore une voiture. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse.
+papa|Merci César.
+narrateur|César ferme la caisse. Ça fait toc. Le sol est libre. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Après le jeu, que fait César ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|César a rangé. Les voitures sont dans la caisse. Le tapis est libre. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|César ferme la caisse. Papa lui tend l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|César ferme la caisse. Ça fait toc. Le sol est libre. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Après le jeu, que fait César ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|César a rangé. Les voitures sont dans la caisse. Le tapis est libre. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1847,7 @@
           <t>narrateur|César ferme la caisse. Papa lui tend l'eau.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>César range les voitures</t>
+          <t>La route de Victorino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorino fait une route sur le tapis. Quand le jeu s'arrête, les voitures rentrent dans la caisse.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>César joue dans sa chambre. Papa est près de la fenêtre. César a des voitures. Les voitures sont rouges et bleues. César fait une route. Les voitures font vroom. Puis le jeu est fini. C'est l'heure de ranger. César prend une voiture. Il la met dans la caisse. Il prend une autre voiture. Il la met dans la caisse. Encore une voiture. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse. Merci César. César ferme la caisse. Ça fait toc. Le sol est libre. Papa sourit.</t>
+          <t>Le rideau de la chambre se soulève un peu. Un oiseau chante sur la branche. Papa est près de la fenêtre. L'air sent l'herbe coupée. Tu as entendu l'oiseau, Victorino ? Oui, papa. Il chante fort. Je range le linge dans le couloir. J'arrive tout de suite. Le tapis de la chambre est épais. En ce moment, Victorino est sur le tapis. Il a des voitures. Les voitures sont rouges et bleues. Victorino fait une route. La route va de la fenêtre jusqu'au lit. Vroom. Vroom. Ta route est longue. Une voiture rouge avance. Une voiture bleue la suit. Les roues font un petit bruit. Ça roule bien, on dirait. Elles vont jusqu'au lit, maman. Puis le jeu est fini. C'est l'heure de ranger. Ranger, c'est mettre dans la caisse. Victorino prend une voiture rouge. Il la met dans la caisse. Toc. Il prend une voiture bleue. Il la met dans la caisse. Toc. Encore une voiture ? Encore une voiture. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse. Merci, Victorino. Victorino ferme la caisse. Ça fait toc. Le sol est libre. Tu as fini de ranger tes jouets ? Oui, maman. Bravo. Tu as fait du bon travail. L'oiseau chante encore un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,53 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|César joue dans sa chambre. Papa est près de la fenêtre. César a des voitures. Les voitures sont rouges et bleues. César fait une route. Les voitures font vroom. Puis le jeu est fini.
+          <t>narrateur|Le rideau de la chambre se soulève un peu.
+narrateur|Un oiseau chante sur la branche.
+narrateur|Papa est près de la fenêtre.
+narrateur|L'air sent l'herbe coupée.
+papa|Tu as entendu l'oiseau, Victorino ?
+enfant-m|Oui, papa. Il chante fort.
+maman|Je range le linge dans le couloir.
+maman|J'arrive tout de suite.
+narrateur|Le tapis de la chambre est épais.
+narrateur|En ce moment, Victorino est sur le tapis.
+narrateur|Il a des voitures.
+narrateur|Les voitures sont rouges et bleues.
+narrateur|Victorino fait une route.
+narrateur|La route va de la fenêtre jusqu'au lit.
+enfant-m|Vroom. Vroom.
+papa|Ta route est longue.
+narrateur|Une voiture rouge avance.
+narrateur|Une voiture bleue la suit.
+narrateur|Les roues font un petit bruit.
+maman|Ça roule bien, on dirait.
+enfant-m|Elles vont jusqu'au lit, maman.
+narrateur|Puis le jeu est fini.
 papa|C'est l'heure de ranger.
-narrateur|César prend une voiture. Il la met dans la caisse. Il prend une autre voiture. Il la met dans la caisse. Encore une voiture. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse.
-papa|Merci César.
-narrateur|César ferme la caisse. Ça fait toc. Le sol est libre. Papa sourit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>voiture_passe</t>
-        </is>
-      </c>
+papa|Ranger, c'est mettre dans la caisse.
+narrateur|Victorino prend une voiture rouge.
+narrateur|Il la met dans la caisse.
+narrateur|Toc.
+narrateur|Il prend une voiture bleue.
+narrateur|Il la met dans la caisse.
+narrateur|Toc.
+maman|Encore une voiture ?
+narrateur|Encore une voiture.
+narrateur|Dans la caisse.
+narrateur|La caisse est pleine.
+narrateur|Le tapis est vide.
+papa|Ranger, c'est mettre dans la caisse.
+papa|Merci, Victorino.
+narrateur|Victorino ferme la caisse.
+narrateur|Ça fait toc.
+narrateur|Le sol est libre.
+maman|Tu as fini de ranger tes jouets ?
+enfant-m|Oui, maman.
+papa|Bravo. Tu as fait du bon travail.
+narrateur|L'oiseau chante encore un peu.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,7 +1395,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Après le jeu, que fait César ?</t>
+          <t>Après le jeu, que fait Victorino ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1551,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Après le jeu, que fait César ?</t>
+          <t>narrateur|Après le jeu, que fait Victorino ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1579,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>César a rangé. Les voitures sont dans la caisse. Le tapis est libre. Papa est là.</t>
+          <t>Victorino a rangé. Les voitures sont dans la caisse. Le tapis est libre. La route est rentrée dans la caisse. J'ai rangé, papa. Oui. Ranger, c'est mettre dans la caisse. Tu as fini de ranger tes jouets ? Oui. Bravo, Victorino. C'est du bon travail. Le rideau bouge encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1723,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|César a rangé. Les voitures sont dans la caisse. Le tapis est libre. Papa est là.</t>
+          <t>narrateur|Victorino a rangé.
+narrateur|Les voitures sont dans la caisse.
+narrateur|Le tapis est libre.
+papa|La route est rentrée dans la caisse.
+enfant-m|J'ai rangé, papa.
+maman|Oui. Ranger, c'est mettre dans la caisse.
+papa|Tu as fini de ranger tes jouets ?
+enfant-m|Oui.
+maman|Bravo, Victorino.
+maman|C'est du bon travail.
+narrateur|Le rideau bouge encore un peu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1761,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>César ferme la caisse. Papa lui tend l'eau.</t>
+          <t>Victorino pousse la caisse sous le lit. Le bois glisse tout doucement. Tu veux un peu d'eau ? Oui, papa. Papa lui tend un verre. Victorino boit une gorgée. La chambre est calme, maintenant. Les voitures dorment. Oui. Dans la caisse. Ils restent près de la fenêtre. On écoute encore l'oiseau ? Oui. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1901,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|César ferme la caisse. Papa lui tend l'eau.</t>
+          <t>narrateur|Victorino pousse la caisse sous le lit.
+narrateur|Le bois glisse tout doucement.
+papa|Tu veux un peu d'eau ?
+enfant-m|Oui, papa.
+narrateur|Papa lui tend un verre.
+narrateur|Victorino boit une gorgée.
+maman|La chambre est calme, maintenant.
+enfant-m|Les voitures dorment.
+papa|Oui. Dans la caisse.
+narrateur|Ils restent près de la fenêtre.
+maman|On écoute encore l'oiseau ?
+enfant-m|Oui.
+papa|Bravo.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1941,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les voitures sont dans la caisse. Bravo. Tu as fait du bon travail. Le tapis est libre. L'oiseau s'en va. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2081,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Les voitures sont dans la caisse.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+maman|Le tapis est libre.
+narrateur|L'oiseau s'en va.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2146,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le rideau de la chambre se soulève un peu. Un oiseau chante sur la branche. Papa est près de la fenêtre. L'air sent l'herbe coupée. Tu as entendu l'oiseau, Victorino ? Oui, papa. Il chante fort. Je range le linge dans le couloir. J'arrive tout de suite. Le tapis de la chambre est épais. En ce moment, Victorino est sur le tapis. Il a des voitures. Les voitures sont rouges et bleues. Victorino fait une route. La route va de la fenêtre jusqu'au lit. Vroom. Vroom. Ta route est longue. Une voiture rouge avance. Une voiture bleue la suit. Les roues font un petit bruit. Ça roule bien, on dirait. Elles vont jusqu'au lit, maman. Puis le jeu est fini. C'est l'heure de ranger. Ranger, c'est mettre dans la caisse. Victorino prend une voiture rouge. Il la met dans la caisse. Toc. Il prend une voiture bleue. Il la met dans la caisse. Toc. Encore une voiture ? Encore une voiture. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse. Merci, Victorino. Victorino ferme la caisse. Ça fait toc. Le sol est libre. Tu as fini de ranger tes jouets ? Oui, maman. Bravo. Tu as fait du bon travail. L'oiseau chante encore un peu.</t>
+          <t>Le rideau de la chambre se soulève un peu. Un oiseau chante sur la branche. Papa est près de la fenêtre. L'air sent l'herbe coupée. Tu as entendu l'oiseau, Victorino ? Oui, papa. Il chante fort. Je plie le linge dans le couloir. J'arrive tout de suite. Le tapis de la chambre est épais. En ce moment, Victorino est sur le tapis. Il a des voitures. Les voitures sont rouges et bleues. Victorino fait une route. La route va de la fenêtre jusqu'au lit. Vroom. Vroom. Ta route est longue. Une voiture rouge avance. Une voiture bleue la suit. Les roues font un petit bruit. Victorino pose les mains en pont. C'est un garage, papa. Un garage au bord de la route. Ça roule bien, on dirait. Elles vont jusqu'au lit, maman. Puis le jeu est fini. C'est l'heure de ranger. Ranger, c'est mettre dans la caisse. Victorino prend une voiture rouge. Il la met dans la caisse. Toc. Il prend une voiture bleue. Il la met dans la caisse. Toc. Encore une voiture ? Encore une voiture. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse. Merci, Victorino. Victorino ferme la caisse. Ça fait toc. Le sol est libre. Tu as fini de ranger tes jouets ? Oui, maman. Bravo. Tu as fait du bon travail. L'oiseau chante encore un peu. La chambre sent l'herbe, un peu. Oui. L'herbe.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
 narrateur|L'air sent l'herbe coupée.
 papa|Tu as entendu l'oiseau, Victorino ?
 enfant-m|Oui, papa. Il chante fort.
-maman|Je range le linge dans le couloir.
+maman|Je plie le linge dans le couloir.
 maman|J'arrive tout de suite.
 narrateur|Le tapis de la chambre est épais.
 narrateur|En ce moment, Victorino est sur le tapis.
@@ -1343,6 +1343,9 @@
 narrateur|Une voiture rouge avance.
 narrateur|Une voiture bleue la suit.
 narrateur|Les roues font un petit bruit.
+narrateur|Victorino pose les mains en pont.
+enfant-m|C'est un garage, papa.
+papa|Un garage au bord de la route.
 maman|Ça roule bien, on dirait.
 enfant-m|Elles vont jusqu'au lit, maman.
 narrateur|Puis le jeu est fini.
@@ -1367,7 +1370,9 @@
 maman|Tu as fini de ranger tes jouets ?
 enfant-m|Oui, maman.
 papa|Bravo. Tu as fait du bon travail.
-narrateur|L'oiseau chante encore un peu.</t>
+narrateur|L'oiseau chante encore un peu.
+papa|La chambre sent l'herbe, un peu.
+enfant-m|Oui. L'herbe.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -2108,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2151,6 +2156,34 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La route de Victorino</t>
+          <t>Le merle du rideau</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Victorino fait une route sur le tapis. Quand le jeu s'arrête, les voitures rentrent dans la caisse.</t>
+          <t>Victorino veut voir l'oiseau depuis le lit. Les voitures barrent le chemin. Il les met dans la caisse. Le rideau s'ouvre.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le rideau de la chambre se soulève un peu. Un oiseau chante sur la branche. Papa est près de la fenêtre. L'air sent l'herbe coupée. Tu as entendu l'oiseau, Victorino ? Oui, papa. Il chante fort. Je plie le linge dans le couloir. J'arrive tout de suite. Le tapis de la chambre est épais. En ce moment, Victorino est sur le tapis. Il a des voitures. Les voitures sont rouges et bleues. Victorino fait une route. La route va de la fenêtre jusqu'au lit. Vroom. Vroom. Ta route est longue. Une voiture rouge avance. Une voiture bleue la suit. Les roues font un petit bruit. Victorino pose les mains en pont. C'est un garage, papa. Un garage au bord de la route. Ça roule bien, on dirait. Elles vont jusqu'au lit, maman. Puis le jeu est fini. C'est l'heure de ranger. Ranger, c'est mettre dans la caisse. Victorino prend une voiture rouge. Il la met dans la caisse. Toc. Il prend une voiture bleue. Il la met dans la caisse. Toc. Encore une voiture ? Encore une voiture. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse. Merci, Victorino. Victorino ferme la caisse. Ça fait toc. Le sol est libre. Tu as fini de ranger tes jouets ? Oui, maman. Bravo. Tu as fait du bon travail. L'oiseau chante encore un peu. La chambre sent l'herbe, un peu. Oui. L'herbe.</t>
+          <t>Une odeur d'orange entre dans la chambre. Maman a pelé un fruit, dans la cuisine. La lumière est couleur de miel. Une abeille bourdonne dehors. Puis elle s'en va. Tu as entendu l'abeille, Victorino ? Oui, papa. Elle est partie. Le rideau est à moitié fermé. Un merle est sur la gouttière. On l'entend un peu. Il chante tout doux. Le tapis de la chambre est épais. En ce moment, Victorino est à genoux. Il a des voitures rouges et bleues. Il fait une route. La route va de la fenêtre jusqu'au lit. Vroom. Vroom. Ta route est longue. Une voiture rouge avance. Une voiture bleue la suit. Les roues font un petit bruit. Victorino souffle. Vroom. La voiture rouge va jusqu'au lit. Puis elle revient. Victorino pose les mains en pont. C'est un garage, papa. Un garage au bord de la route. Après, je veux voir le merle. Depuis le lit, avec le rideau ouvert. Oui. Tout grand. Victorino se lève. Il veut aller au lit. Une voiture bleue est contre le pied du lit. Une voiture rouge est sur le chemin. Je ne peux pas tirer le rideau. Les voitures sont encore au sol. Le merle chante encore un peu. Je ne le vois pas bien. Le chemin du lit est pris.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;César joue dans sa chambre. Papa est près de la fenêtre. César a des voitures. Les voitures sont rouges et bleues. César fait une route. Les voitures font vroom. Puis le jeu est fini. Papa dit : c'est l'heure de &lt;emphasis level="moderate"&gt;ranger&lt;/emphasis&gt;. César prend une voiture. Il la met dans la caisse. Il prend une autre voiture. Il la met dans la caisse. Encore une voiture. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse. Papa dit : merci César. César ferme la caisse. Ça fait toc. Le sol est libre. Papa sourit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une odeur d'orange entre dans la chambre. Maman a pelé un fruit, dans la cuisine. La lumière est couleur de miel. Une abeille bourdonne dehors. Puis elle s'en va. Tu as entendu l'abeille, Victorino ? Oui, papa. Elle est partie. Le rideau est à moitié fermé. Un merle est sur la gouttière. On l'entend un peu. Il chante tout doux. Le tapis de la chambre est épais. En ce moment, Victorino est à genoux. Il a des voitures rouges et bleues. Il fait une route. La route va de la fenêtre jusqu'au lit. Vroom. Vroom. Ta route est longue. Une voiture rouge avance. Une voiture bleue la suit. Les roues font un petit bruit. Victorino souffle. Vroom. La voiture rouge va jusqu'au lit. Puis elle revient. Victorino pose les mains en pont. C'est un garage, papa. Un garage au bord de la route. Après, je veux voir le merle. Depuis le lit, avec le rideau ouvert. Oui. Tout grand. Victorino se lève. Il veut aller au lit. Une voiture bleue est contre le pied du lit. Une voiture rouge est sur le chemin. Je ne peux pas tirer le rideau. Les voitures sont encore au sol. Le merle chante encore un peu. Je ne le vois pas bien. Le chemin du lit est pris.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,58 +1324,47 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le rideau de la chambre se soulève un peu.
-narrateur|Un oiseau chante sur la branche.
-narrateur|Papa est près de la fenêtre.
-narrateur|L'air sent l'herbe coupée.
-papa|Tu as entendu l'oiseau, Victorino ?
-enfant-m|Oui, papa. Il chante fort.
-maman|Je plie le linge dans le couloir.
-maman|J'arrive tout de suite.
+          <t>narrateur|Une odeur d'orange entre dans la chambre.
+narrateur|Maman a pelé un fruit, dans la cuisine.
+narrateur|La lumière est couleur de miel.
+narrateur|Une abeille bourdonne dehors.
+narrateur|Puis elle s'en va.
+papa|Tu as entendu l'abeille, Victorino ?
+enfant-m|Oui, papa. Elle est partie.
+narrateur|Le rideau est à moitié fermé.
+narrateur|Un merle est sur la gouttière.
+narrateur|On l'entend un peu.
+maman|Il chante tout doux.
 narrateur|Le tapis de la chambre est épais.
-narrateur|En ce moment, Victorino est sur le tapis.
-narrateur|Il a des voitures.
-narrateur|Les voitures sont rouges et bleues.
-narrateur|Victorino fait une route.
+narrateur|En ce moment, Victorino est à genoux.
+narrateur|Il a des voitures rouges et bleues.
+narrateur|Il fait une route.
 narrateur|La route va de la fenêtre jusqu'au lit.
 enfant-m|Vroom. Vroom.
 papa|Ta route est longue.
 narrateur|Une voiture rouge avance.
 narrateur|Une voiture bleue la suit.
 narrateur|Les roues font un petit bruit.
+narrateur|Victorino souffle. Vroom.
+narrateur|La voiture rouge va jusqu'au lit.
+narrateur|Puis elle revient.
 narrateur|Victorino pose les mains en pont.
 enfant-m|C'est un garage, papa.
 papa|Un garage au bord de la route.
-maman|Ça roule bien, on dirait.
-enfant-m|Elles vont jusqu'au lit, maman.
-narrateur|Puis le jeu est fini.
-papa|C'est l'heure de ranger.
-papa|Ranger, c'est mettre dans la caisse.
-narrateur|Victorino prend une voiture rouge.
-narrateur|Il la met dans la caisse.
-narrateur|Toc.
-narrateur|Il prend une voiture bleue.
-narrateur|Il la met dans la caisse.
-narrateur|Toc.
-maman|Encore une voiture ?
-narrateur|Encore une voiture.
-narrateur|Dans la caisse.
-narrateur|La caisse est pleine.
-narrateur|Le tapis est vide.
-papa|Ranger, c'est mettre dans la caisse.
-papa|Merci, Victorino.
-narrateur|Victorino ferme la caisse.
-narrateur|Ça fait toc.
-narrateur|Le sol est libre.
-maman|Tu as fini de ranger tes jouets ?
-enfant-m|Oui, maman.
-papa|Bravo. Tu as fait du bon travail.
-narrateur|L'oiseau chante encore un peu.
-papa|La chambre sent l'herbe, un peu.
-enfant-m|Oui. L'herbe.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-m|Après, je veux voir le merle.
+maman|Depuis le lit, avec le rideau ouvert.
+enfant-m|Oui. Tout grand.
+narrateur|Victorino se lève.
+narrateur|Il veut aller au lit.
+narrateur|Une voiture bleue est contre le pied du lit.
+narrateur|Une voiture rouge est sur le chemin.
+enfant-m|Je ne peux pas tirer le rideau.
+papa|Les voitures sont encore au sol.
+narrateur|Le merle chante encore un peu.
+enfant-m|Je ne le vois pas bien.
+maman|Le chemin du lit est pris.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1405,7 +1394,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Après le jeu, que fait César ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Après le jeu, que fait Victorino ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1420,7 +1409,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>ranger | la caisse | dans la caisse | il range</t>
+          <t>ranger | la caisse | dans la caisse | il range | voitures dans la caisse</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1435,7 +1424,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il met les voitures dans la caisse. Que fait César ?</t>
+          <t>Il met les voitures dans la caisse. Que fait Victorino ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1559,7 +1548,6 @@
           <t>narrateur|Après le jeu, que fait Victorino ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1584,12 +1572,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino a rangé. Les voitures sont dans la caisse. Le tapis est libre. La route est rentrée dans la caisse. J'ai rangé, papa. Oui. Ranger, c'est mettre dans la caisse. Tu as fini de ranger tes jouets ? Oui. Bravo, Victorino. C'est du bon travail. Le rideau bouge encore un peu.</t>
+          <t>Victorino prend la voiture bleue. La caisse est sous le lit. Il la met dans la caisse. Toc. Au garage. On va ranger. Tu ranges les voitures. Il prend la voiture rouge. Dans la caisse. Toc. Encore une voiture. Dans la caisse. Le chemin est libre. Victorino va jusqu'au lit. Il tire le rideau. La lumière entre. Le merle ! Sur la gouttière.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;César a rangé. Les voitures sont dans la &lt;emphasis level="moderate"&gt;caisse&lt;/emphasis&gt;. Le tapis est libre. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino prend la voiture bleue. La caisse est sous le lit. Il la met dans la caisse. Toc. Au garage. On va ranger. Tu ranges les voitures. Il prend la voiture rouge. Dans la caisse. Toc. Encore une voiture. Dans la caisse. Le chemin est libre. Victorino va jusqu'au lit. Il tire le rideau. La lumière entre. Le merle ! Sur la gouttière.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1728,20 +1716,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Victorino a rangé.
-narrateur|Les voitures sont dans la caisse.
-narrateur|Le tapis est libre.
-papa|La route est rentrée dans la caisse.
-enfant-m|J'ai rangé, papa.
-maman|Oui. Ranger, c'est mettre dans la caisse.
-papa|Tu as fini de ranger tes jouets ?
-enfant-m|Oui.
-maman|Bravo, Victorino.
-maman|C'est du bon travail.
-narrateur|Le rideau bouge encore un peu.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorino prend la voiture bleue.
+narrateur|La caisse est sous le lit.
+narrateur|Il la met dans la caisse.
+narrateur|Toc.
+enfant-m|Au garage.
+papa|On va ranger.
+papa|Tu ranges les voitures.
+narrateur|Il prend la voiture rouge.
+narrateur|Dans la caisse.
+narrateur|Toc.
+narrateur|Encore une voiture.
+narrateur|Dans la caisse.
+maman|Le chemin est libre.
+narrateur|Victorino va jusqu'au lit.
+narrateur|Il tire le rideau.
+narrateur|La lumière entre.
+enfant-m|Le merle !
+papa|Sur la gouttière.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1766,12 +1760,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Victorino pousse la caisse sous le lit. Le bois glisse tout doucement. Tu veux un peu d'eau ? Oui, papa. Papa lui tend un verre. Victorino boit une gorgée. La chambre est calme, maintenant. Les voitures dorment. Oui. Dans la caisse. Ils restent près de la fenêtre. On écoute encore l'oiseau ? Oui. Bravo.</t>
+          <t>Victorino monte sur le lit. Papa s'assoit près de lui. Le merle tourne la tête. Il me voit. Peut-être. Ça sent encore l'orange. La lumière est couleur de miel. Les voitures dorment. Dans la caisse. Dans le garage. Oui. Sous le lit. Le merle chante une dernière fois. Puis il s'envole. Il reviendra. Oui. Le rideau reste ouvert. Ils restent un moment sur le lit. L'orange sent encore bon. Oui. Tout doux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;César ferme la &lt;emphasis level="moderate"&gt;caisse&lt;/emphasis&gt;. Papa lui tend l'eau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino monte sur le lit. Papa s'assoit près de lui. Le merle tourne la tête. Il me voit. Peut-être. Ça sent encore l'orange. La lumière est couleur de miel. Les voitures dorment. Dans la caisse. Dans le garage. Oui. Sous le lit. Le merle chante une dernière fois. Puis il s'envole. Il reviendra. Oui. Le rideau reste ouvert. Ils restent un moment sur le lit. L'orange sent encore bon. Oui. Tout doux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1906,22 +1900,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Victorino pousse la caisse sous le lit.
-narrateur|Le bois glisse tout doucement.
-papa|Tu veux un peu d'eau ?
-enfant-m|Oui, papa.
-narrateur|Papa lui tend un verre.
-narrateur|Victorino boit une gorgée.
-maman|La chambre est calme, maintenant.
-enfant-m|Les voitures dorment.
-papa|Oui. Dans la caisse.
-narrateur|Ils restent près de la fenêtre.
-maman|On écoute encore l'oiseau ?
-enfant-m|Oui.
-papa|Bravo.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Victorino monte sur le lit.
+narrateur|Papa s'assoit près de lui.
+narrateur|Le merle tourne la tête.
+enfant-m|Il me voit.
+maman|Peut-être.
+narrateur|Ça sent encore l'orange.
+narrateur|La lumière est couleur de miel.
+papa|Les voitures dorment.
+enfant-m|Dans la caisse. Dans le garage.
+maman|Oui. Sous le lit.
+narrateur|Le merle chante une dernière fois.
+narrateur|Puis il s'envole.
+enfant-m|Il reviendra.
+papa|Oui. Le rideau reste ouvert.
+narrateur|Ils restent un moment sur le lit.
+maman|L'orange sent encore bon.
+enfant-m|Oui. Tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1946,12 +1943,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Les voitures sont dans la caisse. Bravo. Tu as fait du bon travail. Le tapis est libre. L'oiseau s'en va. L'histoire est finie.</t>
+          <t>J'ai vu le merle depuis le lit. Le rideau était ouvert. Les voitures sont dans la caisse. La chambre sent encore l'orange. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai vu le merle depuis le lit. Le rideau était ouvert. Les voitures sont dans la caisse. La chambre sent encore l'orange. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2086,15 +2083,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|Les voitures sont dans la caisse.
-papa|Bravo.
-papa|Tu as fait du bon travail.
-maman|Le tapis est libre.
-narrateur|L'oiseau s'en va.
+          <t>enfant-m|J'ai vu le merle depuis le lit.
+maman|Le rideau était ouvert.
+narrateur|Les voitures sont dans la caisse.
+papa|La chambre sent encore l'orange.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2113,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2186,6 +2181,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
@@ -1943,12 +1943,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai vu le merle depuis le lit. Le rideau était ouvert. Les voitures sont dans la caisse. La chambre sent encore l'orange. L'histoire est finie.</t>
+          <t>J'ai vu le merle depuis le lit. Le rideau était ouvert. Les voitures sont dans la caisse. La chambre sent encore l'orange.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai vu le merle depuis le lit. Le rideau était ouvert. Les voitures sont dans la caisse. La chambre sent encore l'orange. L'histoire est finie.</t>
+          <t>J'ai vu le merle depuis le lit. Le rideau était ouvert. Les voitures sont dans la caisse. La chambre sent encore l'orange.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2086,8 +2086,7 @@
           <t>enfant-m|J'ai vu le merle depuis le lit.
 maman|Le rideau était ouvert.
 narrateur|Les voitures sont dans la caisse.
-papa|La chambre sent encore l'orange.
-narrateur|L'histoire est finie.</t>
+papa|La chambre sent encore l'orange.</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2186,6 +2185,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chambre</t>
+          <t>chambre, lumière d'orange, après-midi</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>César, papa</t>
+          <t>Victorino, papa, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le merle du rideau</t>
+          <t>La voiture rouge</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chambre, lumière d'orange, après-midi</t>
+          <t>chambre, lumière de miel, odeur d'orange, merle sur la gouttière</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Victorino veut voir l'oiseau depuis le lit. Les voitures barrent le chemin. Il les met dans la caisse. Le rideau s'ouvre.</t>
+          <t>Victorino veut l'histoire au lit avec sa voiture rouge, et voir le merle. Les autres voitures recouvrent la rouge. Il les met dans la caisse pour chercher. La rouge apparaît. Rideau, orange, merle.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une odeur d'orange entre dans la chambre. Maman a pelé un fruit, dans la cuisine. La lumière est couleur de miel. Une abeille bourdonne dehors. Puis elle s'en va. Tu as entendu l'abeille, Victorino ? Oui, papa. Elle est partie. Le rideau est à moitié fermé. Un merle est sur la gouttière. On l'entend un peu. Il chante tout doux. Le tapis de la chambre est épais. En ce moment, Victorino est à genoux. Il a des voitures rouges et bleues. Il fait une route. La route va de la fenêtre jusqu'au lit. Vroom. Vroom. Ta route est longue. Une voiture rouge avance. Une voiture bleue la suit. Les roues font un petit bruit. Victorino souffle. Vroom. La voiture rouge va jusqu'au lit. Puis elle revient. Victorino pose les mains en pont. C'est un garage, papa. Un garage au bord de la route. Après, je veux voir le merle. Depuis le lit, avec le rideau ouvert. Oui. Tout grand. Victorino se lève. Il veut aller au lit. Une voiture bleue est contre le pied du lit. Une voiture rouge est sur le chemin. Je ne peux pas tirer le rideau. Les voitures sont encore au sol. Le merle chante encore un peu. Je ne le vois pas bien. Le chemin du lit est pris.</t>
+          <t>Une odeur d'orange entre dans la chambre. Maman a pelé un fruit, dans la cuisine. La lumière est couleur de miel. Une abeille bourdonne dehors. Puis elle s'en va. Tu as entendu l'abeille, Victorino ? Oui, papa, elle est partie. Le rideau est à moitié fermé. Un merle est sur la gouttière. On l'entend un peu. Il chante tout doux. Le tapis de la chambre est épais. En ce moment, Victorino est à genoux. Il a des voitures rouges et bleues. Il fait une route. La route va de la fenêtre jusqu'au lit. Vroom. Ta route est longue. La voiture rouge avance en tête. Une voiture bleue la suit. Les roues font un petit bruit. Victorino pose les mains en pont. C'est un garage, papa. Un garage au bord de la route. Après, tu racontes, maman ? Oui, au lit, avec le rideau ouvert. La rouge vient avec moi. Victorino la pousse vers le lit. D'autres voitures se poussent. La bleue passe par-dessus. La rouge disparaît sous la pile. Oh. Elles se sont bousculées. Où est ma voiture rouge ? Sous le lit, peut-être ? Victorino se penche. De la poussière, un chausson. Pas de rouge. Dans le garage ? Il ouvre ses deux mains. Le pont de doigts est vide. Elle est perdue. La route est encore au sol. Je veux voir dessous. Victorino prend une voiture bleue. Il la pose dans la caisse. Toc. Le bois glisse un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Une odeur d'orange entre dans la chambre. Maman a pelé un fruit, dans la cuisine. La lumière est couleur de miel. Une abeille bourdonne dehors. Puis elle s'en va. Tu as entendu l'abeille, Victorino ? Oui, papa. Elle est partie. Le rideau est à moitié fermé. Un merle est sur la gouttière. On l'entend un peu. Il chante tout doux. Le tapis de la chambre est épais. En ce moment, Victorino est à genoux. Il a des voitures rouges et bleues. Il fait une route. La route va de la fenêtre jusqu'au lit. Vroom. Vroom. Ta route est longue. Une voiture rouge avance. Une voiture bleue la suit. Les roues font un petit bruit. Victorino souffle. Vroom. La voiture rouge va jusqu'au lit. Puis elle revient. Victorino pose les mains en pont. C'est un garage, papa. Un garage au bord de la route. Après, je veux voir le merle. Depuis le lit, avec le rideau ouvert. Oui. Tout grand. Victorino se lève. Il veut aller au lit. Une voiture bleue est contre le pied du lit. Une voiture rouge est sur le chemin. Je ne peux pas tirer le rideau. Les voitures sont encore au sol. Le merle chante encore un peu. Je ne le vois pas bien. Le chemin du lit est pris.</t>
+          <t>Une odeur d'orange entre dans la chambre. Maman a pelé un fruit, dans la cuisine. La lumière est couleur de miel. Une abeille bourdonne dehors. Puis elle s'en va. Tu as entendu l'abeille, Victorino ? Oui, papa, elle est partie. Le rideau est à moitié fermé. Un merle est sur la gouttière. On l'entend un peu. Il chante tout doux. Le tapis de la chambre est épais. En ce moment, Victorino est à genoux. Il a des voitures rouges et bleues. Il fait une route. La route va de la fenêtre jusqu'au lit. Vroom. Ta route est longue. La voiture rouge avance en tête. Une voiture bleue la suit. Les roues font un petit bruit. Victorino pose les mains en pont. C'est un garage, papa. Un garage au bord de la route. Après, tu racontes, maman ? Oui, au lit, avec le rideau ouvert. La rouge vient avec moi. Victorino la pousse vers le lit. D'autres voitures se poussent. La bleue passe par-dessus. La rouge disparaît sous la pile. Oh. Elles se sont bousculées. Où est ma voiture rouge ? Sous le lit, peut-être ? Victorino se penche. De la poussière, un chausson. Pas de rouge. Dans le garage ? Il ouvre ses deux mains. Le pont de doigts est vide. Elle est perdue. La route est encore au sol. Je veux voir dessous. Victorino prend une voiture bleue. Il la pose dans la caisse. Toc. Le bois glisse un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
 narrateur|Une abeille bourdonne dehors.
 narrateur|Puis elle s'en va.
 papa|Tu as entendu l'abeille, Victorino ?
-enfant-m|Oui, papa. Elle est partie.
+enfant-m|Oui, papa, elle est partie.
 narrateur|Le rideau est à moitié fermé.
 narrateur|Un merle est sur la gouttière.
 narrateur|On l'entend un peu.
@@ -1340,29 +1340,38 @@
 narrateur|Il a des voitures rouges et bleues.
 narrateur|Il fait une route.
 narrateur|La route va de la fenêtre jusqu'au lit.
-enfant-m|Vroom. Vroom.
+enfant-m|Vroom.
 papa|Ta route est longue.
-narrateur|Une voiture rouge avance.
+narrateur|La voiture rouge avance en tête.
 narrateur|Une voiture bleue la suit.
 narrateur|Les roues font un petit bruit.
-narrateur|Victorino souffle. Vroom.
-narrateur|La voiture rouge va jusqu'au lit.
-narrateur|Puis elle revient.
 narrateur|Victorino pose les mains en pont.
 enfant-m|C'est un garage, papa.
 papa|Un garage au bord de la route.
-enfant-m|Après, je veux voir le merle.
-maman|Depuis le lit, avec le rideau ouvert.
-enfant-m|Oui. Tout grand.
-narrateur|Victorino se lève.
-narrateur|Il veut aller au lit.
-narrateur|Une voiture bleue est contre le pied du lit.
-narrateur|Une voiture rouge est sur le chemin.
-enfant-m|Je ne peux pas tirer le rideau.
-papa|Les voitures sont encore au sol.
-narrateur|Le merle chante encore un peu.
-enfant-m|Je ne le vois pas bien.
-maman|Le chemin du lit est pris.</t>
+enfant-m|Après, tu racontes, maman ?
+maman|Oui, au lit, avec le rideau ouvert.
+enfant-m|La rouge vient avec moi.
+narrateur|Victorino la pousse vers le lit.
+narrateur|D'autres voitures se poussent.
+narrateur|La bleue passe par-dessus.
+narrateur|La rouge disparaît sous la pile.
+enfant-m|Oh.
+papa|Elles se sont bousculées.
+enfant-m|Où est ma voiture rouge ?
+maman|Sous le lit, peut-être ?
+narrateur|Victorino se penche.
+narrateur|De la poussière, un chausson.
+narrateur|Pas de rouge.
+enfant-m|Dans le garage ?
+narrateur|Il ouvre ses deux mains.
+narrateur|Le pont de doigts est vide.
+enfant-m|Elle est perdue.
+papa|La route est encore au sol.
+enfant-m|Je veux voir dessous.
+narrateur|Victorino prend une voiture bleue.
+narrateur|Il la pose dans la caisse.
+narrateur|Toc.
+narrateur|Le bois glisse un peu.</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1398,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Après le jeu, que fait Victorino ?</t>
+          <t>Victorino cherche sa voiture rouge. Où est-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Après le jeu, que fait Victorino ?</t>
+          <t>Victorino cherche sa voiture rouge. Où est-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1404,12 +1413,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>la voiture rouge</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>ranger | la caisse | dans la caisse | il range | voitures dans la caisse</t>
+          <t>la voiture rouge | la rouge | voiture rouge | sous la route | sous les voitures | dessous</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1424,7 +1433,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il met les voitures dans la caisse. Que fait Victorino ?</t>
+          <t>Il cherche sous les voitures. Où est la voiture rouge ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1473,7 +1482,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1545,7 +1554,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Après le jeu, que fait Victorino ?</t>
+          <t>narrateur|Victorino cherche sa voiture rouge.
+narrateur|Où est-elle ?</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1582,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino prend la voiture bleue. La caisse est sous le lit. Il la met dans la caisse. Toc. Au garage. On va ranger. Tu ranges les voitures. Il prend la voiture rouge. Dans la caisse. Toc. Encore une voiture. Dans la caisse. Le chemin est libre. Victorino va jusqu'au lit. Il tire le rideau. La lumière entre. Le merle ! Sur la gouttière.</t>
+          <t>Une autre bleue va dans la caisse. Toc. Tu regardes bien sous la route ? Oui, maman. Un bout de tapis reparaît. Encore une, tout doux. Victorino soulève une voiture noire. Un toit rouge brille dessous. Ma rouge ! La voiture rouge était sous les autres. Elle sent encore le tapis. Victorino la tient dans la paume. Le métal est un peu froid. Merci, tu l'as trouvée. Te voilà, petite rouge. Elle était dessous. Les dernières voitures vont dans la caisse. Le chemin du lit est libre. Le merle chante encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Victorino prend la voiture bleue. La caisse est sous le lit. Il la met dans la caisse. Toc. Au garage. On va ranger. Tu ranges les voitures. Il prend la voiture rouge. Dans la caisse. Toc. Encore une voiture. Dans la caisse. Le chemin est libre. Victorino va jusqu'au lit. Il tire le rideau. La lumière entre. Le merle ! Sur la gouttière.</t>
+          <t>Une autre bleue va dans la caisse. Toc. Tu regardes bien sous la route ? Oui, maman. Un bout de tapis reparaît. Encore une, tout doux. Victorino soulève une voiture noire. Un toit rouge brille dessous. Ma rouge ! La voiture rouge était sous les autres. Elle sent encore le tapis. Victorino la tient dans la paume. Le métal est un peu froid. Merci, tu l'as trouvée. Te voilà, petite rouge. Elle était dessous. Les dernières voitures vont dans la caisse. Le chemin du lit est libre. Le merle chante encore un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1640,7 +1650,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1716,24 +1726,25 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Victorino prend la voiture bleue.
-narrateur|La caisse est sous le lit.
-narrateur|Il la met dans la caisse.
+          <t>narrateur|Une autre bleue va dans la caisse.
 narrateur|Toc.
-enfant-m|Au garage.
-papa|On va ranger.
-papa|Tu ranges les voitures.
-narrateur|Il prend la voiture rouge.
-narrateur|Dans la caisse.
-narrateur|Toc.
-narrateur|Encore une voiture.
-narrateur|Dans la caisse.
-maman|Le chemin est libre.
-narrateur|Victorino va jusqu'au lit.
-narrateur|Il tire le rideau.
-narrateur|La lumière entre.
-enfant-m|Le merle !
-papa|Sur la gouttière.</t>
+maman|Tu regardes bien sous la route ?
+enfant-m|Oui, maman.
+narrateur|Un bout de tapis reparaît.
+papa|Encore une, tout doux.
+narrateur|Victorino soulève une voiture noire.
+narrateur|Un toit rouge brille dessous.
+enfant-m|Ma rouge !
+narrateur|La voiture rouge était sous les autres.
+narrateur|Elle sent encore le tapis.
+narrateur|Victorino la tient dans la paume.
+narrateur|Le métal est un peu froid.
+papa|Merci, tu l'as trouvée.
+maman|Te voilà, petite rouge.
+enfant-m|Elle était dessous.
+narrateur|Les dernières voitures vont dans la caisse.
+narrateur|Le chemin du lit est libre.
+narrateur|Le merle chante encore un peu.</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1771,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Victorino monte sur le lit. Papa s'assoit près de lui. Le merle tourne la tête. Il me voit. Peut-être. Ça sent encore l'orange. La lumière est couleur de miel. Les voitures dorment. Dans la caisse. Dans le garage. Oui. Sous le lit. Le merle chante une dernière fois. Puis il s'envole. Il reviendra. Oui. Le rideau reste ouvert. Ils restent un moment sur le lit. L'orange sent encore bon. Oui. Tout doux.</t>
+          <t>Victorino pousse la caisse sous le lit. Le bois glisse tout doucement. On ouvre le rideau ? Oui, tout grand. Le merle est encore sur la gouttière. Il penche la tête. Victorino grimpe sur le lit. La voiture rouge est sur l'oreiller. Je raconte ? Oui, maman. Maman s'assoit au bord. Sa voix est basse, tout près. Tu veux un quartier d'orange ? Oui, papa. L'orange sent fort, sucrée. Le jus brille un peu sur le doigt. Le merle écoute aussi, on dirait.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Victorino monte sur le lit. Papa s'assoit près de lui. Le merle tourne la tête. Il me voit. Peut-être. Ça sent encore l'orange. La lumière est couleur de miel. Les voitures dorment. Dans la caisse. Dans le garage. Oui. Sous le lit. Le merle chante une dernière fois. Puis il s'envole. Il reviendra. Oui. Le rideau reste ouvert. Ils restent un moment sur le lit. L'orange sent encore bon. Oui. Tout doux.</t>
+          <t>Victorino pousse la caisse sous le lit. Le bois glisse tout doucement. On ouvre le rideau ? Oui, tout grand. Le merle est encore sur la gouttière. Il penche la tête. Victorino grimpe sur le lit. La voiture rouge est sur l'oreiller. Je raconte ? Oui, maman. Maman s'assoit au bord. Sa voix est basse, tout près. Tu veux un quartier d'orange ? Oui, papa. L'orange sent fort, sucrée. Le jus brille un peu sur le doigt. Le merle écoute aussi, on dirait.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1828,7 +1839,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1900,23 +1911,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Victorino monte sur le lit.
-narrateur|Papa s'assoit près de lui.
-narrateur|Le merle tourne la tête.
-enfant-m|Il me voit.
-maman|Peut-être.
-narrateur|Ça sent encore l'orange.
-narrateur|La lumière est couleur de miel.
-papa|Les voitures dorment.
-enfant-m|Dans la caisse. Dans le garage.
-maman|Oui. Sous le lit.
-narrateur|Le merle chante une dernière fois.
-narrateur|Puis il s'envole.
-enfant-m|Il reviendra.
-papa|Oui. Le rideau reste ouvert.
-narrateur|Ils restent un moment sur le lit.
-maman|L'orange sent encore bon.
-enfant-m|Oui. Tout doux.</t>
+          <t>narrateur|Victorino pousse la caisse sous le lit.
+narrateur|Le bois glisse tout doucement.
+enfant-m|On ouvre le rideau ?
+papa|Oui, tout grand.
+narrateur|Le merle est encore sur la gouttière.
+narrateur|Il penche la tête.
+narrateur|Victorino grimpe sur le lit.
+narrateur|La voiture rouge est sur l'oreiller.
+maman|Je raconte ?
+enfant-m|Oui, maman.
+narrateur|Maman s'assoit au bord.
+narrateur|Sa voix est basse, tout près.
+papa|Tu veux un quartier d'orange ?
+enfant-m|Oui, papa.
+narrateur|L'orange sent fort, sucrée.
+narrateur|Le jus brille un peu sur le doigt.
+narrateur|Le merle écoute aussi, on dirait.</t>
         </is>
       </c>
     </row>
@@ -1943,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai vu le merle depuis le lit. Le rideau était ouvert. Les voitures sont dans la caisse. La chambre sent encore l'orange.</t>
+          <t>La rouge est sur l'oreiller. Toi aussi, tu es bien. Bravo, tu l'as retrouvée. L'odeur d'orange reste dans la chambre. Le merle se tait, tout doux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai vu le merle depuis le lit. Le rideau était ouvert. Les voitures sont dans la caisse. La chambre sent encore l'orange.</t>
+          <t>La rouge est sur l'oreiller. Toi aussi, tu es bien. Bravo, tu l'as retrouvée. L'odeur d'orange reste dans la chambre. Le merle se tait, tout doux.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2004,14 +2015,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2083,10 +2094,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'ai vu le merle depuis le lit.
-maman|Le rideau était ouvert.
-narrateur|Les voitures sont dans la caisse.
-papa|La chambre sent encore l'orange.</t>
+          <t>enfant-m|La rouge est sur l'oreiller.
+maman|Toi aussi, tu es bien.
+papa|Bravo, tu l'as retrouvée.
+narrateur|L'odeur d'orange reste dans la chambre.
+narrateur|Le merle se tait, tout doux.</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2192,6 +2204,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chambre, lumière de miel, odeur d'orange, merle sur la gouttière</t>
+          <t>chambre, odeur d'orange, merle sur la gouttière, caisse à éclat d'écorce</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Victorino veut l'histoire au lit avec sa voiture rouge, et voir le merle. Les autres voitures recouvrent la rouge. Il les met dans la caisse pour chercher. La rouge apparaît. Rideau, orange, merle.</t>
+          <t>Le merle glisse sur le rideau. Sur la caisse, un éclat d'écorce luit. Victorino veut la rouge sur l'oreiller, maintenant, pour l'histoire. Il ramasse toute la pile : clac, l'éclat disparaît. Papa s'accroupit. Une par une. Merci vécu. Il refuse de foncer. Sous le lit, l'éclat d'écorce reste pâle.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une odeur d'orange entre dans la chambre. Maman a pelé un fruit, dans la cuisine. La lumière est couleur de miel. Une abeille bourdonne dehors. Puis elle s'en va. Tu as entendu l'abeille, Victorino ? Oui, papa, elle est partie. Le rideau est à moitié fermé. Un merle est sur la gouttière. On l'entend un peu. Il chante tout doux. Le tapis de la chambre est épais. En ce moment, Victorino est à genoux. Il a des voitures rouges et bleues. Il fait une route. La route va de la fenêtre jusqu'au lit. Vroom. Ta route est longue. La voiture rouge avance en tête. Une voiture bleue la suit. Les roues font un petit bruit. Victorino pose les mains en pont. C'est un garage, papa. Un garage au bord de la route. Après, tu racontes, maman ? Oui, au lit, avec le rideau ouvert. La rouge vient avec moi. Victorino la pousse vers le lit. D'autres voitures se poussent. La bleue passe par-dessus. La rouge disparaît sous la pile. Oh. Elles se sont bousculées. Où est ma voiture rouge ? Sous le lit, peut-être ? Victorino se penche. De la poussière, un chausson. Pas de rouge. Dans le garage ? Il ouvre ses deux mains. Le pont de doigts est vide. Elle est perdue. La route est encore au sol. Je veux voir dessous. Victorino prend une voiture bleue. Il la pose dans la caisse. Toc. Le bois glisse un peu.</t>
+          <t>Une ombre d'oiseau glisse sur le rideau. Le merle est sur la gouttière. Au pied du lit, la caisse en bois attend. Un éclat d'écorce luit sur le couvercle. Il brille, papa. Tu le vois, sur le bois ? L'air sent l'orange, depuis la cuisine. J'ai pelé un fruit, Victorino. Le tapis de la chambre est épais. Des voitures rouges et bleues attendent. La rouge va jusqu'au lit, maintenant ! Avec le rideau ouvert, pour l'histoire ? Oui, elle vient sur l'oreiller. Ta route est longue, jusqu'au lit. En ce moment, Victorino pousse la rouge. Les roues font un petit bruit sec. Une bleue la suit, trop près. D'autres voitures se poussent vers le lit. La bleue passe par-dessus la pile. La rouge disparaît sous les toits. Oh ! Le sourire de Victorino disparaît. Où est ma voiture rouge ? Sous le lit, peut-être ? Il se penche, trop vite. De la poussière, un chausson. Pas de rouge. Je prends toute la pile ! Il ramasse les voitures d'un coup. La pile glisse, clac, contre la caisse. Le couvercle bascule. L'éclat d'écorce disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Elles se sont bousculées. Elle est perdue.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Une odeur d'orange entre dans la chambre. Maman a pelé un fruit, dans la cuisine. La lumière est couleur de miel. Une abeille bourdonne dehors. Puis elle s'en va. Tu as entendu l'abeille, Victorino ? Oui, papa, elle est partie. Le rideau est à moitié fermé. Un merle est sur la gouttière. On l'entend un peu. Il chante tout doux. Le tapis de la chambre est épais. En ce moment, Victorino est à genoux. Il a des voitures rouges et bleues. Il fait une route. La route va de la fenêtre jusqu'au lit. Vroom. Ta route est longue. La voiture rouge avance en tête. Une voiture bleue la suit. Les roues font un petit bruit. Victorino pose les mains en pont. C'est un garage, papa. Un garage au bord de la route. Après, tu racontes, maman ? Oui, au lit, avec le rideau ouvert. La rouge vient avec moi. Victorino la pousse vers le lit. D'autres voitures se poussent. La bleue passe par-dessus. La rouge disparaît sous la pile. Oh. Elles se sont bousculées. Où est ma voiture rouge ? Sous le lit, peut-être ? Victorino se penche. De la poussière, un chausson. Pas de rouge. Dans le garage ? Il ouvre ses deux mains. Le pont de doigts est vide. Elle est perdue. La route est encore au sol. Je veux voir dessous. Victorino prend une voiture bleue. Il la pose dans la caisse. Toc. Le bois glisse un peu.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Une ombre d'oiseau glisse sur le rideau. Le merle est sur la gouttière. Au pied du lit, la caisse en bois attend. Un &lt;emphasis level="moderate"&gt;éclat d'écorce&lt;/emphasis&gt; luit sur le couvercle. Il brille, papa. Tu le vois, sur le bois ? L'air sent l'orange, depuis la cuisine. J'ai pelé un fruit, Victorino. Le tapis de la chambre est épais. Des voitures rouges et bleues attendent. La rouge va jusqu'au lit, maintenant ! Avec le rideau ouvert, pour l'histoire ? Oui, elle vient sur l'oreiller. Ta route est longue, jusqu'au lit. En ce moment, Victorino pousse la rouge. Les roues font un petit bruit sec. Une bleue la suit, trop près. D'autres voitures se poussent vers le lit. La bleue passe par-dessus la pile. La rouge disparaît sous les toits. Oh ! Le sourire de Victorino disparaît. Où est ma voiture rouge ? Sous le lit, peut-être ? Il se penche, trop vite. De la poussière, un chausson. Pas de rouge. Je prends toute la pile ! Il ramasse les voitures d'un coup. La pile glisse, clac, contre la caisse. Le couvercle bascule. L'éclat d'écorce disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Elles se sont bousculées. Elle est perdue.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>César joue dans sa chambre. Papa est près de la fenêtre. César a des voitures. Les voitures sont rouges et bleues. César fait une route. Les voitures font vroom. Puis le jeu est fini. Papa dit : c'est l'heure de &lt;emphasis&gt;ranger&lt;/emphasis&gt;. César prend une voiture. Il la met dans la caisse. Il prend une autre voiture. Il la met dans la caisse. Encore une voiture. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse. Papa dit : merci César. César ferme la caisse. Ça fait toc. Le sol est libre. Papa sourit. [pause]</t>
+          <t>Une ombre d'oiseau glisse sur le rideau. Le merle est sur la gouttière. Au pied du lit, la caisse en bois attend. Un &lt;emphasis&gt;éclat d'écorce&lt;/emphasis&gt; luit sur le couvercle. Il brille, papa. Tu le vois, sur le bois ? L'air sent l'orange, depuis la cuisine. J'ai pelé un fruit, Victorino. Le tapis de la chambre est épais. Des voitures rouges et bleues attendent. La rouge va jusqu'au lit, maintenant ! Avec le rideau ouvert, pour l'histoire ? Oui, elle vient sur l'oreiller. Ta route est longue, jusqu'au lit. En ce moment, Victorino pousse la rouge. Les roues font un petit bruit sec. Une bleue la suit, trop près. D'autres voitures se poussent vers le lit. La bleue passe par-dessus la pile. La rouge disparaît sous les toits. Oh ! Le sourire de Victorino disparaît. Où est ma voiture rouge ? Sous le lit, peut-être ? Il se penche, trop vite. De la poussière, un chausson. Pas de rouge. Je prends toute la pile ! Il ramasse les voitures d'un coup. La pile glisse, clac, contre la caisse. Le couvercle bascule. L'éclat d'écorce disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Elles se sont bousculées. Elle est perdue. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>éclat d'écorce</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1321,57 +1321,53 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience_curieuse puis découragement; intensite=2; destinataire=enfant; sous_texte=il_veut_la_rouge_sur_l_oreiller_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Une odeur d'orange entre dans la chambre.
-narrateur|Maman a pelé un fruit, dans la cuisine.
-narrateur|La lumière est couleur de miel.
-narrateur|Une abeille bourdonne dehors.
-narrateur|Puis elle s'en va.
-papa|Tu as entendu l'abeille, Victorino ?
-enfant-m|Oui, papa, elle est partie.
-narrateur|Le rideau est à moitié fermé.
-narrateur|Un merle est sur la gouttière.
-narrateur|On l'entend un peu.
-maman|Il chante tout doux.
+          <t>narrateur|Une ombre d'oiseau glisse sur le rideau.
+narrateur|Le merle est sur la gouttière.
+narrateur|Au pied du lit, la caisse en bois attend.
+narrateur|Un éclat d'écorce luit sur le couvercle.
+enfant-m|Il brille, papa.
+papa|Tu le vois, sur le bois ?
+narrateur|L'air sent l'orange, depuis la cuisine.
+maman|J'ai pelé un fruit, Victorino.
 narrateur|Le tapis de la chambre est épais.
-narrateur|En ce moment, Victorino est à genoux.
-narrateur|Il a des voitures rouges et bleues.
-narrateur|Il fait une route.
-narrateur|La route va de la fenêtre jusqu'au lit.
-enfant-m|Vroom.
-papa|Ta route est longue.
-narrateur|La voiture rouge avance en tête.
-narrateur|Une voiture bleue la suit.
-narrateur|Les roues font un petit bruit.
-narrateur|Victorino pose les mains en pont.
-enfant-m|C'est un garage, papa.
-papa|Un garage au bord de la route.
-enfant-m|Après, tu racontes, maman ?
-maman|Oui, au lit, avec le rideau ouvert.
-enfant-m|La rouge vient avec moi.
-narrateur|Victorino la pousse vers le lit.
-narrateur|D'autres voitures se poussent.
-narrateur|La bleue passe par-dessus.
-narrateur|La rouge disparaît sous la pile.
-enfant-m|Oh.
-papa|Elles se sont bousculées.
+narrateur|Des voitures rouges et bleues attendent.
+enfant-m|La rouge va jusqu'au lit, maintenant !
+maman|Avec le rideau ouvert, pour l'histoire ?
+enfant-m|Oui, elle vient sur l'oreiller.
+papa|Ta route est longue, jusqu'au lit.
+narrateur|En ce moment, Victorino pousse la rouge.
+narrateur|Les roues font un petit bruit sec.
+narrateur|Une bleue la suit, trop près.
+narrateur|D'autres voitures se poussent vers le lit.
+narrateur|La bleue passe par-dessus la pile.
+narrateur|La rouge disparaît sous les toits.
+enfant-m|Oh !
+narrateur|Le sourire de Victorino disparaît.
 enfant-m|Où est ma voiture rouge ?
 maman|Sous le lit, peut-être ?
-narrateur|Victorino se penche.
+narrateur|Il se penche, trop vite.
 narrateur|De la poussière, un chausson.
 narrateur|Pas de rouge.
-enfant-m|Dans le garage ?
-narrateur|Il ouvre ses deux mains.
-narrateur|Le pont de doigts est vide.
-enfant-m|Elle est perdue.
-papa|La route est encore au sol.
-enfant-m|Je veux voir dessous.
-narrateur|Victorino prend une voiture bleue.
-narrateur|Il la pose dans la caisse.
-narrateur|Toc.
-narrateur|Le bois glisse un peu.</t>
+enfant-m|Je prends toute la pile !
+narrateur|Il ramasse les voitures d'un coup.
+narrateur|La pile glisse, clac, contre la caisse.
+narrateur|Le couvercle bascule.
+narrateur|L'éclat d'écorce disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+papa|Elles se sont bousculées.
+enfant-m|Elle est perdue.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>rideau,merle,orange,voitures</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1399,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Victorino cherche sa voiture rouge. Où est-elle ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Victorino cherche sa &lt;emphasis level="moderate"&gt;voiture rouge&lt;/emphasis&gt;. Où est-elle ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Après le jeu, que fait César ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Victorino cherche sa &lt;emphasis&gt;voiture rouge&lt;/emphasis&gt;. Où est-elle ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1471,7 +1467,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1482,7 +1478,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1497,34 +1493,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>voiture rouge</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1539,17 +1539,17 @@
         <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=elle_est_sous_les_autres; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1582,17 +1582,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Une autre bleue va dans la caisse. Toc. Tu regardes bien sous la route ? Oui, maman. Un bout de tapis reparaît. Encore une, tout doux. Victorino soulève une voiture noire. Un toit rouge brille dessous. Ma rouge ! La voiture rouge était sous les autres. Elle sent encore le tapis. Victorino la tient dans la paume. Le métal est un peu froid. Merci, tu l'as trouvée. Te voilà, petite rouge. Elle était dessous. Les dernières voitures vont dans la caisse. Le chemin du lit est libre. Le merle chante encore un peu.</t>
+          <t>Papa s'accroupit à la même hauteur. Tu regardes bien sous la route ? Oui, papa. Victorino pose une bleue dans la caisse. Toc. Un bout de tapis reparaît. Une par une, Victorino. Il soulève une voiture noire. Un toit rouge brille dessous. Ma rouge ! La voiture rouge était sous les autres. Elle sent le tapis, un peu froide. Merci, tu l'as trouvée. Le couvercle de la caisse se rassoit. L'éclat d'écorce reparaît, pâle. Il est revenu. Te voilà, petite rouge. Elle était dessous. Victorino la tient dans la paume. Il essuie le tapis du toit, du pouce. Le chemin du lit est presque libre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Une autre bleue va dans la caisse. Toc. Tu regardes bien sous la route ? Oui, maman. Un bout de tapis reparaît. Encore une, tout doux. Victorino soulève une voiture noire. Un toit rouge brille dessous. Ma rouge ! La voiture rouge était sous les autres. Elle sent encore le tapis. Victorino la tient dans la paume. Le métal est un peu froid. Merci, tu l'as trouvée. Te voilà, petite rouge. Elle était dessous. Les dernières voitures vont dans la caisse. Le chemin du lit est libre. Le merle chante encore un peu.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa s'accroupit à la même hauteur. Tu regardes bien sous la route ? Oui, papa. Victorino pose une bleue dans la caisse. Toc. Un bout de tapis reparaît. Une par une, Victorino. Il soulève une voiture noire. Un toit rouge brille dessous. Ma rouge ! La voiture rouge était sous les autres. Elle sent le tapis, un peu froide. Merci, tu l'as trouvée. Le couvercle de la caisse se rassoit. L'&lt;emphasis level="moderate"&gt;éclat d'écorce&lt;/emphasis&gt; reparaît, pâle. Il est revenu. Te voilà, petite rouge. Elle était dessous. Victorino la tient dans la paume. Il essuie le tapis du toit, du pouce. Le chemin du lit est presque libre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>César a rangé. Les voitures sont dans la &lt;emphasis&gt;caisse&lt;/emphasis&gt;. Le tapis est libre. Papa est là. [pause]</t>
+          <t>Papa s'accroupit à la même hauteur. Tu regardes bien sous la route ? Oui, papa. Victorino pose une bleue dans la caisse. Toc. Un bout de tapis reparaît. Une par une, Victorino. Il soulève une voiture noire. Un toit rouge brille dessous. Ma rouge ! La voiture rouge était sous les autres. Elle sent le tapis, un peu froide. Merci, tu l'as trouvée. Le couvercle de la caisse se rassoit. L'&lt;emphasis&gt;éclat d'écorce&lt;/emphasis&gt; reparaît, pâle. Il est revenu. Te voilà, petite rouge. Elle était dessous. Victorino la tient dans la paume. Il essuie le tapis du toit, du pouce. Le chemin du lit est presque libre. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1650,7 +1650,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>caisse</t>
+          <t>éclat d'écorce</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
@@ -1687,16 +1687,16 @@
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1721,30 +1721,37 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=confirmation; intention=relancer; emotion=soulagement_prudent; intensite=1; destinataire=enfant; sous_texte=une_par_une_le_toit_rouge_reparaît; tempo=naturel; sourire=léger; respiration=fluide</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Une autre bleue va dans la caisse.
+          <t>narrateur|Papa s'accroupit à la même hauteur.
+papa|Tu regardes bien sous la route ?
+enfant-m|Oui, papa.
+narrateur|Victorino pose une bleue dans la caisse.
 narrateur|Toc.
-maman|Tu regardes bien sous la route ?
-enfant-m|Oui, maman.
 narrateur|Un bout de tapis reparaît.
-papa|Encore une, tout doux.
-narrateur|Victorino soulève une voiture noire.
+maman|Une par une, Victorino.
+narrateur|Il soulève une voiture noire.
 narrateur|Un toit rouge brille dessous.
 enfant-m|Ma rouge !
 narrateur|La voiture rouge était sous les autres.
-narrateur|Elle sent encore le tapis.
-narrateur|Victorino la tient dans la paume.
-narrateur|Le métal est un peu froid.
+narrateur|Elle sent le tapis, un peu froide.
 papa|Merci, tu l'as trouvée.
+narrateur|Le couvercle de la caisse se rassoit.
+narrateur|L'éclat d'écorce reparaît, pâle.
+enfant-m|Il est revenu.
 maman|Te voilà, petite rouge.
 enfant-m|Elle était dessous.
-narrateur|Les dernières voitures vont dans la caisse.
-narrateur|Le chemin du lit est libre.
-narrateur|Le merle chante encore un peu.</t>
+narrateur|Victorino la tient dans la paume.
+narrateur|Il essuie le tapis du toit, du pouce.
+papa|Le chemin du lit est presque libre.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>caisse,voitures</t>
         </is>
       </c>
     </row>
@@ -1771,17 +1778,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Victorino pousse la caisse sous le lit. Le bois glisse tout doucement. On ouvre le rideau ? Oui, tout grand. Le merle est encore sur la gouttière. Il penche la tête. Victorino grimpe sur le lit. La voiture rouge est sur l'oreiller. Je raconte ? Oui, maman. Maman s'assoit au bord. Sa voix est basse, tout près. Tu veux un quartier d'orange ? Oui, papa. L'orange sent fort, sucrée. Le jus brille un peu sur le doigt. Le merle écoute aussi, on dirait.</t>
+          <t>Les dernières voitures restent en tas. Je les pousse toutes, maintenant ! Il avance les mains vers le tas. Puis il s'arrête net. Il refuse de foncer. Attends, je regarde. Papa attend, sans parler. Victorino observe la caisse, écoute la chambre. Sur le couvercle, l'éclat d'écorce luit. Là, près de l'éclat. Il soulève la dernière bleue, tout près. Rien dessous, seulement le tapis. Les dernières voitures vont dans la caisse. Toc. On ouvre le rideau ? Oui, tout grand. La rouge vient avec toi ? Oui, sur l'oreiller. Victorino pousse la caisse sous le lit. Le bois glisse, l'éclat d'écorce aussi. Un filet de soleil entre sur le tapis. Victorino grimpe sur le lit. La voiture rouge est sur l'oreiller. Je raconte ? Oui, maman.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Victorino pousse la caisse sous le lit. Le bois glisse tout doucement. On ouvre le rideau ? Oui, tout grand. Le merle est encore sur la gouttière. Il penche la tête. Victorino grimpe sur le lit. La voiture rouge est sur l'oreiller. Je raconte ? Oui, maman. Maman s'assoit au bord. Sa voix est basse, tout près. Tu veux un quartier d'orange ? Oui, papa. L'orange sent fort, sucrée. Le jus brille un peu sur le doigt. Le merle écoute aussi, on dirait.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Les dernières voitures restent en tas. Je les pousse toutes, maintenant ! Il avance les mains vers le tas. Puis il s'arrête net. Il refuse de foncer. Attends, je regarde. Papa attend, sans parler. Victorino observe la caisse, écoute la chambre. Sur le couvercle, l'&lt;emphasis level="moderate"&gt;éclat d'écorce&lt;/emphasis&gt; luit. Là, près de l'éclat. Il soulève la dernière bleue, tout près. Rien dessous, seulement le tapis. Les dernières voitures vont dans la caisse. Toc. On ouvre le rideau ? Oui, tout grand. La rouge vient avec toi ? Oui, sur l'oreiller. Victorino pousse la caisse sous le lit. Le bois glisse, l'éclat d'écorce aussi. Un filet de soleil entre sur le tapis. Victorino grimpe sur le lit. La voiture rouge est sur l'oreiller. Je raconte ? Oui, maman.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>César ferme la &lt;emphasis&gt;caisse&lt;/emphasis&gt;. Papa lui tend l'eau. [pause]</t>
+          <t>Les dernières voitures restent en tas. Je les pousse toutes, maintenant ! Il avance les mains vers le tas. Puis il s'arrête net. Il refuse de foncer. Attends, je regarde. Papa attend, sans parler. Victorino observe la caisse, écoute la chambre. Sur le couvercle, l'&lt;emphasis&gt;éclat d'écorce&lt;/emphasis&gt; luit. Là, près de l'éclat. Il soulève la dernière bleue, tout près. Rien dessous, seulement le tapis. Les dernières voitures vont dans la caisse. Toc. On ouvre le rideau ? Oui, tout grand. La rouge vient avec toi ? Oui, sur l'oreiller. Victorino pousse la caisse sous le lit. Le bois glisse, l'éclat d'écorce aussi. Un filet de soleil entre sur le tapis. Victorino grimpe sur le lit. La voiture rouge est sur l'oreiller. Je raconte ? Oui, maman. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1828,7 +1835,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1836,10 +1843,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1862,30 +1869,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>caisse</t>
+          <t>éclat d'écorce</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1894,10 +1901,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1908,26 +1915,43 @@
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=entraîner; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=il_refuse_de_foncer_sans_regarder_l_eclat; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Victorino pousse la caisse sous le lit.
-narrateur|Le bois glisse tout doucement.
-enfant-m|On ouvre le rideau ?
-papa|Oui, tout grand.
-narrateur|Le merle est encore sur la gouttière.
-narrateur|Il penche la tête.
+          <t>narrateur|Les dernières voitures restent en tas.
+enfant-m|Je les pousse toutes, maintenant !
+narrateur|Il avance les mains vers le tas.
+narrateur|Puis il s'arrête net.
+narrateur|Il refuse de foncer.
+enfant-m|Attends, je regarde.
+narrateur|Papa attend, sans parler.
+narrateur|Victorino observe la caisse, écoute la chambre.
+narrateur|Sur le couvercle, l'éclat d'écorce luit.
+enfant-m|Là, près de l'éclat.
+narrateur|Il soulève la dernière bleue, tout près.
+narrateur|Rien dessous, seulement le tapis.
+narrateur|Les dernières voitures vont dans la caisse.
+narrateur|Toc.
+maman|On ouvre le rideau ?
+enfant-m|Oui, tout grand.
+papa|La rouge vient avec toi ?
+enfant-m|Oui, sur l'oreiller.
+narrateur|Victorino pousse la caisse sous le lit.
+narrateur|Le bois glisse, l'éclat d'écorce aussi.
+narrateur|Un filet de soleil entre sur le tapis.
 narrateur|Victorino grimpe sur le lit.
 narrateur|La voiture rouge est sur l'oreiller.
 maman|Je raconte ?
-enfant-m|Oui, maman.
-narrateur|Maman s'assoit au bord.
-narrateur|Sa voix est basse, tout près.
-papa|Tu veux un quartier d'orange ?
-enfant-m|Oui, papa.
-narrateur|L'orange sent fort, sucrée.
-narrateur|Le jus brille un peu sur le doigt.
-narrateur|Le merle écoute aussi, on dirait.</t>
+enfant-m|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>caisse,rideau</t>
         </is>
       </c>
     </row>
@@ -1954,17 +1978,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La rouge est sur l'oreiller. Toi aussi, tu es bien. Bravo, tu l'as retrouvée. L'odeur d'orange reste dans la chambre. Le merle se tait, tout doux.</t>
+          <t>Maman s'assoit au bord du lit. Sa voix est basse, tout près. Tu veux un quartier d'orange ? Oui, papa. L'orange sent fort, sucrée. Le jus brille un peu sur le doigt. La rouge a un petit éclat. Un éclat d'écorce tient sur le toit. Tu le vois, comme sur la caisse ? Oui, maman. Le merle penche la tête, dehors. Sous le lit, l'éclat d'écorce reste pâle.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>La rouge est sur l'oreiller. Toi aussi, tu es bien. Bravo, tu l'as retrouvée. L'odeur d'orange reste dans la chambre. Le merle se tait, tout doux.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Maman s'assoit au bord du lit. Sa voix est basse, tout près. Tu veux un quartier d'orange ? Oui, papa. L'orange sent fort, sucrée. Le jus brille un peu sur le doigt. La rouge a un petit éclat. Un &lt;emphasis level="moderate"&gt;éclat d'écorce&lt;/emphasis&gt; tient sur le toit. Tu le vois, comme sur la caisse ? Oui, maman. Le merle penche la tête, dehors. Sous le lit, l'éclat d'écorce reste pâle.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Maman s'assoit au bord du lit. Sa voix est basse, tout près. Tu veux un quartier d'orange ? Oui, papa. L'orange sent fort, sucrée. Le jus brille un peu sur le doigt. La rouge a un petit éclat. Un &lt;emphasis&gt;éclat d'écorce&lt;/emphasis&gt; tient sur le toit. Tu le vois, comme sur la caisse ? Oui, maman. Le merle penche la tête, dehors. Sous le lit, l'éclat d'écorce reste pâle.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2011,18 +2035,18 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2031,12 +2055,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2045,17 +2069,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat d'écorce</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2064,11 +2092,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2077,28 +2105,44 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse et fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_sur_le_toit_rouge; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|La rouge est sur l'oreiller.
-maman|Toi aussi, tu es bien.
-papa|Bravo, tu l'as retrouvée.
-narrateur|L'odeur d'orange reste dans la chambre.
-narrateur|Le merle se tait, tout doux.</t>
+          <t>narrateur|Maman s'assoit au bord du lit.
+narrateur|Sa voix est basse, tout près.
+papa|Tu veux un quartier d'orange ?
+enfant-m|Oui, papa.
+narrateur|L'orange sent fort, sucrée.
+narrateur|Le jus brille un peu sur le doigt.
+enfant-m|La rouge a un petit éclat.
+narrateur|Un éclat d'écorce tient sur le toit.
+maman|Tu le vois, comme sur la caisse ?
+enfant-m|Oui, maman.
+narrateur|Le merle penche la tête, dehors.
+narrateur|Sous le lit, l'éclat d'écorce reste pâle.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>orange,merle</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2211,6 +2255,13 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
